--- a/consulting_forms/004_practice_launch_pre_consult_questionnaire--consulting_forms.xlsx
+++ b/consulting_forms/004_practice_launch_pre_consult_questionnaire--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Do you have any existing relationships with clients?</t>
+          <t>What is your current role or job function?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is the client's budget?</t>
+          <t>How many years of experience do you have in your field?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What is the client's budget?</t>
+          <t>What is your current work location or industry?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -617,20 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What is the client's budget?</t>
+          <t>Do you have any existing relationships with clients?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What are the client's goals?</t>
+          <t>What is the client's preferred consulting style?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Do you have any existing relationships with clients?</t>
+          <t>What are the client's top goals for our consultation?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,11 +686,103 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is the client's budget?</t>
+          <t>Additional notes or any other information?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>practice_launch_pre_consult_questionnaire_page_9</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Do you have any additional comments or questions?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>practice_launch_pre_consult_questionnaire_page_10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Do you have any other information that would be helpful for our consultation?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>practice_launch_pre_consult_questionnaire_page_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Practice Launch Pre Consult Questionnaire Page 11</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>practice_launch_pre_consult_questionnaire_page_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Practice Launch Pre Consult Questionnaire Page 12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -735,136 +827,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>practice_launch_pre_consult_questionnaire_page_2_choices</t>
+          <t>practice_launch_pre_consult_questionnaire_page_5_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>consultant</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>practice_launch_pre_consult_questionnaire_page_2_choices</t>
+          <t>practice_launch_pre_consult_questionnaire_page_5_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>practice_launch_pre_consult_questionnaire_page_5_choices</t>
+          <t>practice_launch_pre_consult_questionnaire_page_6_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>low-key</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Low-key</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>practice_launch_pre_consult_questionnaire_page_5_choices</t>
+          <t>practice_launch_pre_consult_questionnaire_page_6_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>medium-key</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Medium-key</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>practice_launch_pre_consult_questionnaire_page_5_choices</t>
+          <t>practice_launch_pre_consult_questionnaire_page_6_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>high-key</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>practice_launch_pre_consult_questionnaire_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>client_a</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Client A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>practice_launch_pre_consult_questionnaire_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>client_b</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Client B</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>practice_launch_pre_consult_questionnaire_page_7_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>client_c</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Client C</t>
+          <t>High-key</t>
         </is>
       </c>
     </row>
